--- a/etf_holdings/2026-08-25_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:17</t>
+          <t>2026-08-25 10:25:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:18</t>
+          <t>2026-08-25 10:25:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:19</t>
+          <t>2026-08-25 10:25:06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:21</t>
+          <t>2026-08-25 10:25:08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:21</t>
+          <t>2026-08-25 10:25:08</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:21</t>
+          <t>2026-08-25 10:25:08</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:21</t>
+          <t>2026-08-25 10:25:08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:21</t>
+          <t>2026-08-25 10:25:08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.45%2375</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2375</v>
+        <v>2400</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.98%588,000</t>
+          <t>13.92%588,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.98%</t>
+          <t>13.92%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.44%341</t>
+          <t>+1.91%347.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>341</v>
+        <v>347.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.85%1,448,000</t>
+          <t>4.92%1,448,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.85%</t>
+          <t>4.92%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.4%250.5</t>
+          <t>-1.8%246</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>250.5</v>
+        <v>246</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.31%1,737,000</t>
+          <t>4.34%1,737,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.98%101.5</t>
+          <t>+0.99%102.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.81%2,828,000</t>
+          <t>3.85%2,828,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.72%6300</t>
+          <t>+2.22%6440</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6300</v>
+        <v>6440</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.27%53,000</t>
+          <t>3.33%53,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.45%5155</t>
+          <t>-1.93%2030</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.45%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5155</v>
+        <v>2030</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.61%49,000</t>
+          <t>2.56%124,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>49000</v>
+        <v>124000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.72%2070</t>
+          <t>+0.97%5205</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2070</v>
+        <v>5205</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.49%124,000</t>
+          <t>2.52%49,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>124000</v>
+        <v>49000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.83%71.5</t>
+          <t>-0.98%70.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>71.5</v>
+        <v>70.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-4.83%355</t>
+          <t>+6.76%379</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-4.83%</t>
+          <t>+6.76%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.41%656,000</t>
+          <t>2.32%656,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3081聯亞光電工業</t>
+          <t>7750新代科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-5.31%2765</t>
+          <t>+9.81%2350</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>+9.81%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2765</v>
+        <v>2350</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.39%83,000</t>
+          <t>2.30%108,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>83000</v>
+        <v>108000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7750新代科技</t>
+          <t>3081聯亞光電工業</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.39%2140</t>
+          <t>+7.05%2960</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>+7.05%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2140</v>
+        <v>2960</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.36%108,000</t>
+          <t>2.29%83,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>108000</v>
+        <v>83000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.26%1460</t>
+          <t>+9.93%1605</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.26%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1460</v>
+        <v>1605</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.23%148,000</t>
+          <t>2.15%148,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.39%51</t>
+          <t>-0.78%50.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.08%4,181,000</t>
+          <t>2.13%4,181,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:04</t>
+          <t>2026-08-25 17:37:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.34%6255</t>
+          <t>-0.17%591</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6255</v>
+        <v>591</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.96%31,000</t>
+          <t>1.98%335,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>31000</v>
+        <v>335000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3711日月光投資控股</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.85%592</t>
+          <t>-0.72%6210</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>592</v>
+        <v>6210</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.94%335,000</t>
+          <t>1.93%31,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>335000</v>
+        <v>31000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.35%2855</t>
+          <t>+3.33%2950</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2855</v>
+        <v>2950</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.92%68,000</t>
+          <t>1.93%68,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.66%3765</t>
+          <t>-0.8%3735</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3765</v>
+        <v>3735</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.87%50,000</t>
+          <t>1.88%50,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.49%20.5</t>
+          <t>-0.49%20.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.77%8,783,000</t>
+          <t>1.79%8,783,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.92%1075</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1075</v>
+        <v>1095</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>6446藥華醫藥</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.67%200.5</t>
+          <t>+1.02%1490</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>200.5</v>
+        <v>1490</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.60%788,000</t>
+          <t>1.59%108,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>788000</v>
+        <v>108000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.32%157</t>
+          <t>+7.64%169</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+7.64%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.57%1,019,000</t>
+          <t>1.59%1,019,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6446藥華醫藥</t>
+          <t>2059川湖科技</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+5.36%1475</t>
+          <t>-0.87%14285</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+5.36%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1475</v>
+        <v>14285</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.49%108,000</t>
+          <t>1.58%11,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>108000</v>
+        <v>11000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2059川湖科技</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+7.66%14410</t>
+          <t>-1%198.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>14410</v>
+        <v>198.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.45%11,000</t>
+          <t>1.57%788,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>11000</v>
+        <v>788000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.86%1735</t>
+          <t>-1.44%1710</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1735</v>
+        <v>1710</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,25 +2029,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2383台光電子材料</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.4%5430</t>
+          <t>+6.11%1215</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5430</v>
+        <v>1215</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.29%23,000</t>
+          <t>1.29%113,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,11 +2056,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>23000</v>
+        <v>113000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.13%77.4</t>
+          <t>+0.65%77.9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>77.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.27%1,657,000</t>
+          <t>1.28%1,657,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>2383台光電子材料</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+5.05%1145</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1145</v>
+        <v>5595</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.22%113,000</t>
+          <t>1.24%23,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>113000</v>
+        <v>23000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.11%501</t>
+          <t>+1.82%670</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>501</v>
+        <v>670</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.01%193,000</t>
+          <t>0.96%146,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>193000</v>
+        <v>146000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:05</t>
+          <t>2026-08-25 17:37:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.39%658</t>
+          <t>+1.8%510</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.94%146,000</t>
+          <t>0.96%193,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>146000</v>
+        <v>193000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.76%948</t>
+          <t>+2.43%971</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>948</v>
+        <v>971</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>+5.39%1270</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>+5.39%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5385</v>
+        <v>1270</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.66%12,000</t>
+          <t>0.67%56,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>12000</v>
+        <v>56000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.84%1205</t>
+          <t>+6.22%5720</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>+6.22%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1205</v>
+        <v>5720</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.66%56,000</t>
+          <t>0.64%12,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>56000</v>
+        <v>12000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>+2.2%1160</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1135</v>
+        <v>1160</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.54%551</t>
+          <t>-1.27%544</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.25%435.5</t>
+          <t>+1.95%444</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>435.5</v>
+        <v>444</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.21%177</t>
+          <t>-2.34%2085</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>177</v>
+        <v>2085</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.43%243,000</t>
+          <t>0.43%20,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>243000</v>
+        <v>20000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+2.89%2135</t>
+          <t>+1.13%179</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+2.89%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2135</v>
+        <v>179</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.41%20,000</t>
+          <t>0.43%243,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>20000</v>
+        <v>243000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.08%2335</t>
+          <t>-3.21%2260</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2335</v>
+        <v>2260</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.27%12,000</t>
+          <t>0.28%12,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2881富邦金融控股</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.49%132</t>
+          <t>+1.21%125</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.20%154,000</t>
+          <t>0.21%171,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>154000</v>
+        <v>171000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2891中國信託金融控股</t>
+          <t>1802台灣玻璃工業</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.15%63.6</t>
+          <t>+1.93%58</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>63.6</v>
+        <v>58</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.20%306,000</t>
+          <t>0.20%357,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>306000</v>
+        <v>357000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2303聯華電子</t>
+          <t>2881富邦金融控股</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+6.01%123.5</t>
+          <t>+7.2%141.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+6.01%</t>
+          <t>+7.2%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>123.5</v>
+        <v>141.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.20%171,000</t>
+          <t>0.20%154,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>171000</v>
+        <v>154000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1802台灣玻璃工業</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.22%56.9</t>
+          <t>+1.42%64.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>56.9</v>
+        <v>64.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.20%357,000</t>
+          <t>0.19%306,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>357000</v>
+        <v>306000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3665貿聯控股（BizLink Holding In</t>
+          <t>2049上銀科技</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-9.89%2050</t>
+          <t>+0.58%345.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-9.89%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2050</v>
+        <v>345.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.20%9,000</t>
+          <t>0.19%55,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9000</v>
+        <v>55000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:06</t>
+          <t>2026-08-25 17:37:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,34 +3188,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2049上銀科技</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.58%343.5</t>
+          <t>-0.23%2195</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>343.5</v>
+        <v>2195</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.19%55,000</t>
+          <t>0.18%8,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>55000</v>
+        <v>8000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:08</t>
+          <t>2026-08-25 17:37:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,34 +3249,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3529力旺電子</t>
+          <t>3665貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.09%2200</t>
+          <t>+1.22%2075</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2200</v>
+        <v>2075</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.17%8,000</t>
+          <t>0.18%9,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:08</t>
+          <t>2026-08-25 17:37:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.81%243.5</t>
+          <t>-0.21%243</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>243.5</v>
+        <v>243</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:08</t>
+          <t>2026-08-25 17:37:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.43%2070</t>
+          <t>-5.07%1965</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-5.07%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2070</v>
+        <v>1965</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:08</t>
+          <t>2026-08-25 17:37:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+7.33%1010</t>
+          <t>-2.97%980</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+7.33%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1010</v>
+        <v>980</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.09%10,000</t>
+          <t>0.10%10,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:08</t>
+          <t>2026-08-25 17:37:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.1%794</t>
+          <t>+5.16%835</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+5.16%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>794</v>
+        <v>835</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:40</t>
+          <t>2026-08-25 21:10:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:41</t>
+          <t>2026-08-25 21:10:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:42</t>
+          <t>2026-08-25 21:10:03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:44</t>
+          <t>2026-08-25 21:10:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:44</t>
+          <t>2026-08-25 21:10:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:44</t>
+          <t>2026-08-25 21:10:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:44</t>
+          <t>2026-08-25 21:10:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:44</t>
+          <t>2026-08-25 21:10:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:00</t>
+          <t>2026-08-25 21:31:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:02</t>
+          <t>2026-08-25 21:31:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:03</t>
+          <t>2026-08-25 21:32:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:04</t>
+          <t>2026-08-25 21:32:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:04</t>
+          <t>2026-08-25 21:32:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:04</t>
+          <t>2026-08-25 21:32:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:04</t>
+          <t>2026-08-25 21:32:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:04</t>
+          <t>2026-08-25 21:32:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:58</t>
+          <t>2026-08-25 22:04:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:59</t>
+          <t>2026-08-25 22:04:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:00</t>
+          <t>2026-08-25 22:04:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:01</t>
+          <t>2026-08-25 22:04:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:01</t>
+          <t>2026-08-25 22:04:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:01</t>
+          <t>2026-08-25 22:04:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:01</t>
+          <t>2026-08-25 22:04:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:01</t>
+          <t>2026-08-25 22:04:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
